--- a/www/terminologies/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251029120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -382,6 +382,36 @@
   </si>
   <si>
     <t>Test rapide d'orientation diagnostique</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-rougeole:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Rougeole</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-dengue:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Dengue</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-chikungunya:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Chikungunya</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-zika:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Zika</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-westnile:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : West Nile</t>
   </si>
   <si>
     <t/>
@@ -754,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1150,15 +1180,55 @@
         <v>122</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1185,79 +1255,79 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>101</v>
@@ -1265,50 +1335,50 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1335,26 +1405,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1381,26 +1451,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J10-XdsFormatCode-CISIS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="159">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20251029120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2025-10-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -382,36 +382,6 @@
   </si>
   <si>
     <t>Test rapide d'orientation diagnostique</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:mso-rougeole:2026</t>
-  </si>
-  <si>
-    <t>Déclaration de maladie à signalement obligatoire : Rougeole</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:mso-dengue:2026</t>
-  </si>
-  <si>
-    <t>Déclaration de maladie à signalement obligatoire : Dengue</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:mso-chikungunya:2026</t>
-  </si>
-  <si>
-    <t>Déclaration de maladie à signalement obligatoire : Chikungunya</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:mso-zika:2026</t>
-  </si>
-  <si>
-    <t>Déclaration de maladie à signalement obligatoire : Zika</t>
-  </si>
-  <si>
-    <t>urn:ans:ci-sis:mso-westnile:2026</t>
-  </si>
-  <si>
-    <t>Déclaration de maladie à signalement obligatoire : West Nile</t>
   </si>
   <si>
     <t/>
@@ -784,7 +754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1180,55 +1150,15 @@
         <v>122</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1255,79 +1185,79 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>101</v>
@@ -1335,50 +1265,50 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1405,26 +1335,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1451,26 +1381,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
